--- a/Behind/june 2026/GT_JUNE_26/05-06-26/bilal Tso.xlsx
+++ b/Behind/june 2026/GT_JUNE_26/05-06-26/bilal Tso.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14A6067-AB50-4CEB-A7BE-53C605CCC3BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03C7E8B-7747-4830-B9B3-AF38BA4ACD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,14 +31,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1854,145 +1846,163 @@
     <xf numFmtId="43" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2006,24 +2016,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2134,7 +2126,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Cust. Price List"/>
@@ -2896,9 +2888,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2936,9 +2928,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2971,26 +2963,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3023,26 +2998,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3350,30 +3308,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>8</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -3384,24 +3342,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -3412,45 +3370,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -3461,17 +3419,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -3482,32 +3440,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -3515,23 +3473,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -3539,7 +3497,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>50</v>
       </c>
@@ -3549,21 +3507,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -3575,14 +3533,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -3590,7 +3548,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -3602,11 +3560,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -3618,19 +3576,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -3647,9 +3605,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -3665,7 +3623,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -3675,7 +3633,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -4204,14 +4162,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -4278,104 +4236,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -4390,39 +4348,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -4437,10 +4395,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -4450,55 +4408,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -4510,6 +4432,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0A00-000000000000}">
@@ -4567,30 +4525,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>9</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -4601,24 +4559,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -4629,45 +4587,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -4678,17 +4636,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -4699,32 +4657,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -4732,23 +4690,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="167"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -4756,7 +4714,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -4766,21 +4724,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -4792,14 +4750,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -4807,7 +4765,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -4819,11 +4777,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -4835,19 +4793,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -4864,9 +4822,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -4882,7 +4840,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -4892,7 +4850,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -5421,14 +5379,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -5495,104 +5453,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -5607,39 +5565,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -5654,10 +5612,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -5667,55 +5625,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -5727,6 +5649,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0B00-000000000000}">
@@ -5784,30 +5742,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>10</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -5818,24 +5776,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -5846,45 +5804,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -5895,17 +5853,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -5916,32 +5874,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -5949,23 +5907,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -5973,7 +5931,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -5983,21 +5941,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -6009,14 +5967,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -6024,7 +5982,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -6036,11 +5994,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -6052,19 +6010,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -6081,9 +6039,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -6099,7 +6057,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -6109,7 +6067,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -6638,14 +6596,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -6712,104 +6670,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -6824,39 +6782,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -6871,10 +6829,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -6884,55 +6842,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -6944,6 +6866,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0C00-000000000000}">
@@ -7001,30 +6959,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>10</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -7035,24 +6993,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -7063,45 +7021,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -7112,17 +7070,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -7133,32 +7091,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -7166,23 +7124,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -7190,7 +7148,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>50</v>
       </c>
@@ -7200,21 +7158,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -7226,14 +7184,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -7241,7 +7199,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -7253,11 +7211,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -7269,19 +7227,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -7298,9 +7256,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -7316,7 +7274,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -7326,7 +7284,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -7855,14 +7813,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -7929,104 +7887,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -8041,39 +7999,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -8088,10 +8046,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -8101,55 +8059,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -8161,6 +8083,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0D00-000000000000}">
@@ -8218,30 +8176,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>10</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -8252,24 +8210,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -8280,45 +8238,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -8329,17 +8287,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -8350,32 +8308,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -8383,7 +8341,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -8392,16 +8350,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -8409,7 +8367,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -8419,21 +8377,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -8445,14 +8403,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -8460,7 +8418,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64" t="s">
         <v>101</v>
       </c>
@@ -8474,11 +8432,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -8490,19 +8448,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -8519,9 +8477,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -8537,7 +8495,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -8547,7 +8505,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -9076,14 +9034,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -9150,104 +9108,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -9262,39 +9220,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -9309,10 +9267,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -9322,55 +9280,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -9382,6 +9304,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0E00-000000000000}">
@@ -12191,30 +12149,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>1</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -12225,24 +12183,24 @@
       </c>
     </row>
     <row r="4" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -12253,43 +12211,43 @@
       </c>
     </row>
     <row r="5" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="201" t="s">
+      <c r="A5" s="241" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
+      <c r="B5" s="241"/>
+      <c r="C5" s="241"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="201"/>
-      <c r="B6" s="201"/>
-      <c r="C6" s="201"/>
+      <c r="A6" s="241"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -12300,17 +12258,17 @@
       </c>
     </row>
     <row r="7" spans="1:21 16383:16384" s="73" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -12321,32 +12279,32 @@
       </c>
     </row>
     <row r="8" spans="1:21 16383:16384" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:21 16383:16384" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -12354,21 +12312,21 @@
       </c>
     </row>
     <row r="10" spans="1:21 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203"/>
+      <c r="A10" s="224"/>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -12376,67 +12334,67 @@
       </c>
     </row>
     <row r="11" spans="1:21 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76"/>
       <c r="C11" s="77"/>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:21 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203"/>
+      <c r="A12" s="224"/>
       <c r="B12" s="76"/>
       <c r="C12" s="77"/>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
-      <c r="T12" s="212" t="s">
+      <c r="T12" s="196" t="s">
         <v>106</v>
       </c>
-      <c r="U12" s="213"/>
+      <c r="U12" s="197"/>
       <c r="XFD12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:21 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
       <c r="L13" s="79">
         <v>0.05</v>
       </c>
-      <c r="T13" s="214"/>
-      <c r="U13" s="215"/>
+      <c r="T13" s="198"/>
+      <c r="U13" s="199"/>
       <c r="XFD13" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:21 16383:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -12448,19 +12406,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="206" t="s">
+      <c r="G14" s="234" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="207"/>
-      <c r="I14" s="207" t="s">
+      <c r="H14" s="235"/>
+      <c r="I14" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="207" t="s">
+      <c r="J14" s="235" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="207"/>
-      <c r="L14" s="209"/>
-      <c r="M14" s="210" t="s">
+      <c r="K14" s="235"/>
+      <c r="L14" s="237"/>
+      <c r="M14" s="229" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -12485,9 +12443,9 @@
       </c>
     </row>
     <row r="15" spans="1:21 16383:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -12503,7 +12461,7 @@
       <c r="H15" s="171" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="208"/>
+      <c r="I15" s="236"/>
       <c r="J15" s="171" t="s">
         <v>78</v>
       </c>
@@ -12513,7 +12471,7 @@
       <c r="L15" s="174" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="211"/>
+      <c r="M15" s="231"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -13176,14 +13134,14 @@
       </c>
     </row>
     <row r="25" spans="1:21 16384:16384" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="218"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="202"/>
       <c r="G25" s="176">
         <f t="shared" ref="G25:M25" si="3">SUM(G16:G24)</f>
         <v>0</v>
@@ -13268,104 +13226,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:21 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152" t="e">
         <f>I25</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153" t="e">
         <f>L25</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="30" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154" t="e">
         <f>K25</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153" t="e">
         <f>P28-P29-P30</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="32" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -13380,39 +13338,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153" t="e">
         <f>P31+P32</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -13427,10 +13385,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160" t="e">
         <f>P33+P34</f>
         <v>#REF!</v>
@@ -13440,19 +13398,50 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
     <mergeCell ref="T12:U13"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
@@ -13469,37 +13458,6 @@
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -13560,30 +13518,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>1</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -13594,24 +13552,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -13622,45 +13580,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>118</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -13671,17 +13629,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A7" s="202"/>
-      <c r="B7" s="202"/>
-      <c r="C7" s="202"/>
+      <c r="A7" s="238"/>
+      <c r="B7" s="238"/>
+      <c r="C7" s="238"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFD7" t="s">
@@ -13689,7 +13647,7 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A8" s="203" t="s">
+      <c r="A8" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B8" s="75" t="s">
@@ -13698,16 +13656,16 @@
       <c r="C8" s="75"/>
       <c r="F8" s="70"/>
       <c r="G8" s="71"/>
-      <c r="K8" s="198" t="s">
+      <c r="K8" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="197" t="s">
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="197"/>
-      <c r="P8" s="197"/>
+      <c r="O8" s="227"/>
+      <c r="P8" s="227"/>
       <c r="R8" s="70"/>
       <c r="S8" s="71"/>
       <c r="XFD8" t="s">
@@ -13715,7 +13673,7 @@
       </c>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="203"/>
+      <c r="A9" s="224"/>
       <c r="B9" s="76" t="s">
         <v>48</v>
       </c>
@@ -13725,21 +13683,21 @@
       </c>
       <c r="F9" s="70"/>
       <c r="G9" s="71"/>
-      <c r="K9" s="198" t="s">
+      <c r="K9" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="197" t="s">
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="197"/>
-      <c r="P9" s="197"/>
+      <c r="O9" s="227"/>
+      <c r="P9" s="227"/>
       <c r="R9" s="70"/>
       <c r="S9" s="71"/>
     </row>
     <row r="10" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B10" s="76" t="s">
@@ -13751,14 +13709,14 @@
       </c>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197"/>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -13766,7 +13724,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="240"/>
+      <c r="A11" s="225"/>
       <c r="B11" s="168"/>
       <c r="J11" s="78"/>
       <c r="K11" s="78"/>
@@ -13778,11 +13736,11 @@
       </c>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="241" t="s">
+      <c r="A12" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="210"/>
-      <c r="C12" s="204" t="s">
+      <c r="B12" s="229"/>
+      <c r="C12" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="80" t="s">
@@ -13794,19 +13752,19 @@
       <c r="F12" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="247" t="s">
+      <c r="G12" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H12" s="248"/>
-      <c r="I12" s="249" t="s">
+      <c r="H12" s="245"/>
+      <c r="I12" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="247" t="s">
+      <c r="J12" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K12" s="251"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="249" t="s">
+      <c r="K12" s="248"/>
+      <c r="L12" s="245"/>
+      <c r="M12" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N12" s="83" t="s">
@@ -13823,9 +13781,9 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="242"/>
-      <c r="B13" s="211"/>
-      <c r="C13" s="205"/>
+      <c r="A13" s="230"/>
+      <c r="B13" s="231"/>
+      <c r="C13" s="233"/>
       <c r="D13" s="86" t="s">
         <v>76</v>
       </c>
@@ -13841,7 +13799,7 @@
       <c r="H13" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="250"/>
+      <c r="I13" s="247"/>
       <c r="J13" s="88" t="s">
         <v>78</v>
       </c>
@@ -13851,7 +13809,7 @@
       <c r="L13" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M13" s="250"/>
+      <c r="M13" s="247"/>
       <c r="N13" s="92">
         <f>IF(B10="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -14423,14 +14381,14 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="222" t="s">
+      <c r="A23" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="223"/>
-      <c r="C23" s="224"/>
-      <c r="D23" s="218"/>
-      <c r="E23" s="218"/>
-      <c r="F23" s="252"/>
+      <c r="B23" s="207"/>
+      <c r="C23" s="208"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="243"/>
       <c r="G23" s="135">
         <f t="shared" ref="G23:M23" si="10">SUM(G14:G22)</f>
         <v>90</v>
@@ -14500,104 +14458,104 @@
       <c r="H25" s="151"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B26" s="225" t="s">
+      <c r="B26" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="226"/>
-      <c r="D26" s="226"/>
-      <c r="E26" s="226"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="226"/>
-      <c r="H26" s="226"/>
-      <c r="I26" s="226"/>
-      <c r="J26" s="226"/>
-      <c r="K26" s="226"/>
-      <c r="L26" s="227"/>
-      <c r="N26" s="234" t="s">
+      <c r="C26" s="210"/>
+      <c r="D26" s="210"/>
+      <c r="E26" s="210"/>
+      <c r="F26" s="210"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="210"/>
+      <c r="I26" s="210"/>
+      <c r="J26" s="210"/>
+      <c r="K26" s="210"/>
+      <c r="L26" s="211"/>
+      <c r="N26" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O26" s="235"/>
+      <c r="O26" s="219"/>
       <c r="P26" s="152">
         <f>I23</f>
         <v>397176</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="228"/>
-      <c r="C27" s="229"/>
-      <c r="D27" s="229"/>
-      <c r="E27" s="229"/>
-      <c r="F27" s="229"/>
-      <c r="G27" s="229"/>
-      <c r="H27" s="229"/>
-      <c r="I27" s="229"/>
-      <c r="J27" s="229"/>
-      <c r="K27" s="229"/>
-      <c r="L27" s="230"/>
-      <c r="N27" s="236" t="s">
+      <c r="B27" s="212"/>
+      <c r="C27" s="213"/>
+      <c r="D27" s="213"/>
+      <c r="E27" s="213"/>
+      <c r="F27" s="213"/>
+      <c r="G27" s="213"/>
+      <c r="H27" s="213"/>
+      <c r="I27" s="213"/>
+      <c r="J27" s="213"/>
+      <c r="K27" s="213"/>
+      <c r="L27" s="214"/>
+      <c r="N27" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O27" s="237"/>
+      <c r="O27" s="221"/>
       <c r="P27" s="153">
         <f>L23</f>
         <v>52309.320000000007</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="228"/>
-      <c r="C28" s="229"/>
-      <c r="D28" s="229"/>
-      <c r="E28" s="229"/>
-      <c r="F28" s="229"/>
-      <c r="G28" s="229"/>
-      <c r="H28" s="229"/>
-      <c r="I28" s="229"/>
-      <c r="J28" s="229"/>
-      <c r="K28" s="229"/>
-      <c r="L28" s="230"/>
-      <c r="N28" s="236" t="s">
+      <c r="B28" s="212"/>
+      <c r="C28" s="213"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="213"/>
+      <c r="F28" s="213"/>
+      <c r="G28" s="213"/>
+      <c r="H28" s="213"/>
+      <c r="I28" s="213"/>
+      <c r="J28" s="213"/>
+      <c r="K28" s="213"/>
+      <c r="L28" s="214"/>
+      <c r="N28" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O28" s="237"/>
+      <c r="O28" s="221"/>
       <c r="P28" s="154">
         <f>K23</f>
         <v>3844.5400000000009</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
       <c r="M29" s="2"/>
-      <c r="N29" s="236" t="s">
+      <c r="N29" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>P26-P27-P28</f>
         <v>341022.14</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
       <c r="M30" s="2"/>
       <c r="N30" s="155" t="s">
         <v>89</v>
@@ -14612,39 +14570,39 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="238" t="s">
+      <c r="N31" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O31" s="239"/>
+      <c r="O31" s="223"/>
       <c r="P31" s="153">
         <f>P29+P30</f>
         <v>417902.56229999999</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="231"/>
-      <c r="C32" s="232"/>
-      <c r="D32" s="232"/>
-      <c r="E32" s="232"/>
-      <c r="F32" s="232"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="232"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="233"/>
+      <c r="B32" s="215"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="216"/>
+      <c r="I32" s="216"/>
+      <c r="J32" s="216"/>
+      <c r="K32" s="216"/>
+      <c r="L32" s="217"/>
       <c r="M32" s="157"/>
       <c r="N32" s="158" t="s">
         <v>91</v>
@@ -14659,10 +14617,10 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N33" s="216" t="s">
+      <c r="N33" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O33" s="217"/>
+      <c r="O33" s="201"/>
       <c r="P33" s="160">
         <f>P31+P32</f>
         <v>419992.07511149999</v>
@@ -14672,57 +14630,31 @@
       <c r="B34" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="219"/>
-      <c r="J34" s="220"/>
-      <c r="K34" s="221"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="202"/>
+      <c r="F34" s="202"/>
+      <c r="G34" s="202"/>
+      <c r="H34" s="202"/>
+      <c r="I34" s="203"/>
+      <c r="J34" s="204"/>
+      <c r="K34" s="205"/>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="243" t="s">
+      <c r="B36" s="249" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="244"/>
-      <c r="D36" s="244"/>
-      <c r="E36" s="244"/>
-      <c r="F36" s="244"/>
-      <c r="G36" s="244"/>
-      <c r="H36" s="244"/>
-      <c r="I36" s="245"/>
+      <c r="C36" s="250"/>
+      <c r="D36" s="250"/>
+      <c r="E36" s="250"/>
+      <c r="F36" s="250"/>
+      <c r="G36" s="250"/>
+      <c r="H36" s="250"/>
+      <c r="I36" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="B26:L32"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
@@ -14739,6 +14671,32 @@
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B26:L32"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N31:O31"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -14796,30 +14754,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>4</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -14830,24 +14788,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -14858,45 +14816,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -14907,17 +14865,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -14928,32 +14886,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -14961,23 +14919,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="169"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -14985,7 +14943,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>50</v>
       </c>
@@ -14995,21 +14953,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -15021,14 +14979,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -15036,7 +14994,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="56"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -15048,11 +15006,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -15064,19 +15022,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -15093,9 +15051,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -15111,7 +15069,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -15121,7 +15079,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -15650,14 +15608,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -15724,104 +15682,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -15836,39 +15794,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -15883,10 +15841,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -15896,55 +15854,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -15956,6 +15878,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -16012,30 +15970,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>3</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -16046,24 +16004,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -16074,45 +16032,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -16123,17 +16081,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -16144,32 +16102,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -16177,7 +16135,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -16186,16 +16144,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -16203,7 +16161,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -16213,21 +16171,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -16239,14 +16197,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -16254,7 +16212,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -16266,11 +16224,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -16282,19 +16240,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -16311,9 +16269,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -16329,7 +16287,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -16339,7 +16297,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.18</v>
@@ -16868,14 +16826,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -16942,104 +16900,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -17054,39 +17012,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -17101,10 +17059,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -17114,55 +17072,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -17174,6 +17096,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -17231,30 +17189,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>5</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -17265,24 +17223,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -17293,45 +17251,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -17342,17 +17300,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -17363,32 +17321,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -17396,7 +17354,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="169" t="s">
@@ -17405,16 +17363,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -17422,7 +17380,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -17432,21 +17390,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -17458,14 +17416,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -17473,7 +17431,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -17485,11 +17443,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -17501,19 +17459,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -17530,9 +17488,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -17548,7 +17506,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -17558,7 +17516,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -18087,14 +18045,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -18161,104 +18119,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -18273,39 +18231,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -18320,10 +18278,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -18333,55 +18291,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -18393,6 +18315,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -18450,30 +18408,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>6</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -18484,24 +18442,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -18512,45 +18470,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -18561,17 +18519,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -18582,32 +18540,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -18615,7 +18573,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -18624,16 +18582,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -18641,7 +18599,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -18651,21 +18609,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -18677,14 +18635,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -18692,7 +18650,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -18704,11 +18662,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -18720,19 +18678,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -18749,9 +18707,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -18767,7 +18725,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -18777,7 +18735,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -19306,14 +19264,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -19380,104 +19338,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -19492,39 +19450,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -19539,10 +19497,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -19552,55 +19510,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -19612,6 +19534,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0800-000000000000}">
@@ -19669,30 +19627,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>7</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -19703,24 +19661,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46294</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -19731,45 +19689,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="252" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="252"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46293</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -19780,17 +19738,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -19801,32 +19759,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -19834,7 +19792,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="169">
@@ -19843,16 +19801,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -19860,7 +19818,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -19870,21 +19828,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -19896,14 +19854,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -19911,7 +19869,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -19923,11 +19881,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -19939,19 +19897,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="247" t="s">
+      <c r="G14" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="248"/>
-      <c r="I14" s="249" t="s">
+      <c r="H14" s="245"/>
+      <c r="I14" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="247" t="s">
+      <c r="J14" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="251"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249" t="s">
+      <c r="K14" s="248"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="246" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -19968,9 +19926,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -19986,7 +19944,7 @@
       <c r="H15" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="250"/>
+      <c r="I15" s="247"/>
       <c r="J15" s="88" t="s">
         <v>78</v>
       </c>
@@ -19996,7 +19954,7 @@
       <c r="L15" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="250"/>
+      <c r="M15" s="247"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -20525,14 +20483,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="252"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -20599,104 +20557,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -20711,39 +20669,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -20758,10 +20716,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -20771,55 +20729,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -20831,6 +20753,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0900-000000000000}">
